--- a/ra/dataCounters/counters.xlsx
+++ b/ra/dataCounters/counters.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\uni\masters nu\RA\pythonCode\ra\dataCounters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C861516-E117-4F6F-BB2E-F87951EE7246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC38E07-D2E2-49D5-8579-64BC21CCA0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -736,6 +739,898 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Log Count of</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" baseline="0"/>
+              <a:t> Rotation Matrices vs N</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>LE Rot. Matrices</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="41275" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$O$2:$O$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2.1492191126553797</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.8075350280688531</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.3092041796704077</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.7154183225950561</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.0570191243227658</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.3518735766208998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.611298362296429</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.8429273560990236</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.0521589186766507</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.242953663274962</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.4183046065321445</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.5805292569017242</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.7314590214827037</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.8725664726779767</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.0050534670785991</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6.1299137474529397</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.2479784189776355</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.3599496355798379</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.4664259866779652</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0C58-405E-A377-7A3D7DD26BC5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>NE Rot. Matrices</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="41275" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$T$2:$T$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0.77815125038364363</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0413926851582251</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2304489213782739</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3802112417116059</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.505149978319906</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.6127838567197355</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.7075701760979363</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7923916894982539</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8692317197309762</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.9395192526186185</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.0043213737826426</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.0644579892269186</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.12057393120585</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.173186268412274</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.2227164711475833</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.2695129442179165</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.3138672203691533</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.3560258571931225</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.3961993470957363</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0C58-405E-A377-7A3D7DD26BC5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Featherstone Rot. Matrices</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="41275" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$Y$2:$Y$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0.3010299956639812</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.47712125471966244</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.6020599913279624</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.69897000433601886</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.77815125038364363</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.84509804001425681</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.90308998699194354</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.95424250943932487</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0413926851582251</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0791812460476249</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.1139433523068367</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.146128035678238</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.1760912590556813</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.2041199826559248</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.2304489213782739</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.255272505103306</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.2787536009528289</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.3010299956639813</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0C58-405E-A377-7A3D7DD26BC5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1130468127"/>
+        <c:axId val="1128951231"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1130468127"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>N, Number of Links</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1128951231"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1128951231"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>Log</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1" baseline="0"/>
+                  <a:t> Count of </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Rotation Matrices</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1130468127"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.1210531614790612"/>
+          <c:y val="0.13356479174280428"/>
+          <c:w val="0.15576215216764974"/>
+          <c:h val="0.19585191091619877"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -1451,7 +2346,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1490,7 +2385,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -1945,7 +2840,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -4715,7 +5609,7 @@
             <c:v>LE Add</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="41275" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -4872,7 +5766,7 @@
             <c:v>NE Add</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="41275" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
@@ -5029,7 +5923,7 @@
             <c:v>Featherstone Add</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="41275" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
@@ -5509,7 +6403,1797 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Log Time vs N</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>NE Log Add Count</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'[1]5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$R$2:$R$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1.3424226808222062</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5563025007672873</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.6989700043360187</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.8061799739838871</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.8920946026904804</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.9637878273455553</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.0253058652647704</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.0791812460476247</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.1271047983648077</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.1702617153949575</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.2095150145426308</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.2455126678141499</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.2787536009528289</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.3096301674258988</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.3384564936046046</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.3654879848908998</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.3909351071033793</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.4149733479708178</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.4377505628203879</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D186-4E6F-BA4D-F8FB9A5D9ED3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>LE Log Add Count</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'[1]5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$M$2:$M$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1.3010299956639813</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7708520116421442</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.1553360374650619</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.4742162640762553</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.7450747915820575</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.9800033715837464</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.1872386198314788</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.3725438007590705</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.5400790888041729</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.6929350025311378</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.8334658601706924</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.9635044994142907</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.0845047832462278</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.1976388755555698</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.3038653488427041</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.4039779636693543</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.4986413188336947</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.5884173812019249</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.6737855508358148</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D186-4E6F-BA4D-F8FB9A5D9ED3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Featherstone Log Add Count</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'[1]5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$W$2:$W$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1.0413926851582251</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.255272505103306</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3979400086720377</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.505149978319906</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5910646070264991</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.6627578316815741</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.7242758696007889</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7781512503836436</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8260748027008264</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.8692317197309762</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.9084850188786497</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.9444826721501687</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.9777236052888478</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.0086001717619175</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.0374264979406238</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.0644579892269186</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.0899051114393981</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.1139433523068369</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.1367205671564067</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D186-4E6F-BA4D-F8FB9A5D9ED3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="732662447"/>
+        <c:axId val="732663887"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="732662447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>N, Number</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1" baseline="0"/>
+                  <a:t> of Links</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="732663887"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="732663887"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>Log Time</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="732662447"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13053999828968746"/>
+          <c:y val="0.11762405856546715"/>
+          <c:w val="0.10201027786493486"/>
+          <c:h val="0.1965019209542527"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Log Count of</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" baseline="0"/>
+              <a:t> Multiplications vs N</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>LE Multiplications</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="41275" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$N$2:$N$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2.0530784434834195</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.6937269489236471</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.1835545336188615</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.5787537844264348</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.9103575572728775</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.1963420201397685</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.4479638302267448</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.672734971642158</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.875923205849455</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.0613695329844326</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.2319637524310654</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.389936494915041</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.5370467492426405</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.6747068607520914</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.8040685213250036</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.926083542306575</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.0415478190213152</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.151133789808104</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.2554148338586577</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F1F7-458C-87BB-5B7EA60AD675}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>NE Multiplications</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="41275" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$S$2:$S$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1.5910646070264991</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7993405494535817</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.9444826721501687</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.0569048513364727</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.1492191126553797</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.2278867046136734</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.2966651902615309</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.357934847000454</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.4132997640812519</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.4638929889859074</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.510545010206612</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.5538830266438746</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.5943925503754266</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.6324572921847245</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.6683859166900001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.7024305364455254</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.7347998295888472</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.7656685547590141</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.7951845896824241</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F1F7-458C-87BB-5B7EA60AD675}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Featherstone Multiplications</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="41275" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$X$2:$X$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1.3802112417116059</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.568201724066995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.6989700043360187</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7993405494535817</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.8808135922807914</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.9493900066449128</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.0086001717619175</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.0606978403536118</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.1072099696478683</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.1492191126553797</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.1875207208364631</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.2227164711475833</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.255272505103306</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.2855573090077739</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.3138672203691533</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.3404441148401185</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.3654879848908998</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.3891660843645326</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.4116197059632301</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-F1F7-458C-87BB-5B7EA60AD675}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1130468127"/>
+        <c:axId val="1128951231"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1130468127"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>N, Number of Links</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1128951231"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1128951231"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>Log</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1" baseline="0"/>
+                  <a:t> Count of Multiplications</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1130468127"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.1210531614790612"/>
+          <c:y val="0.13356479174280428"/>
+          <c:w val="0.15576215216764974"/>
+          <c:h val="0.19585191091619877"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5789,6 +8473,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -6305,8 +9069,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -6333,8 +9097,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -6414,6 +9178,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -6424,6 +9193,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -6435,7 +9209,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -6455,6 +9229,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6467,10 +9244,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -6510,23 +9287,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -6631,8 +9407,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -6764,20 +9540,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -6791,17 +9566,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -6821,7 +9585,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7337,7 +10101,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7853,7 +10617,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -8369,7 +11133,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -8885,7 +11649,1542 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -9663,7 +13962,478 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>190501</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>14289</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{556C8A02-F890-4703-B65D-72DB8802FA11}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00B6A088-96B8-4E81-9BC9-785A418FA5C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Chart 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{993B3ECB-0193-4C2F-9E56-387FE653A696}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="100s"/>
+      <sheetName val="5s"/>
+      <sheetName val="5s 500"/>
+      <sheetName val="10s 1000"/>
+      <sheetName val="20s 2000"/>
+      <sheetName val="30s 3000"/>
+      <sheetName val="40s 4000"/>
+      <sheetName val="50s 5000"/>
+      <sheetName val="60s 6000"/>
+      <sheetName val="70s 7000"/>
+      <sheetName val="80s 8000"/>
+      <sheetName val="90s 9000"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="2">
+          <cell r="A2">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>19</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>20</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3">
+        <row r="1">
+          <cell r="E1" t="str">
+            <v>Log NE</v>
+          </cell>
+          <cell r="F1" t="str">
+            <v>Log LE</v>
+          </cell>
+          <cell r="G1" t="str">
+            <v>Log Ftst</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4">
+        <row r="2">
+          <cell r="E2">
+            <v>0.17912072960929923</v>
+          </cell>
+          <cell r="F2">
+            <v>0.36068075590673898</v>
+          </cell>
+          <cell r="G2">
+            <v>-0.38806437495987745</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="E3">
+            <v>0.26688993247105292</v>
+          </cell>
+          <cell r="F3">
+            <v>0.98361730349472876</v>
+          </cell>
+          <cell r="G3">
+            <v>-0.2277516600281464</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="E4">
+            <v>0.40859607646278268</v>
+          </cell>
+          <cell r="F4">
+            <v>1.4609198138946675</v>
+          </cell>
+          <cell r="G4">
+            <v>-8.6981316252039753E-2</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="E5">
+            <v>0.53064785352748556</v>
+          </cell>
+          <cell r="F5">
+            <v>1.8612580333896194</v>
+          </cell>
+          <cell r="G5">
+            <v>-9.7499670721832143E-3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="E6">
+            <v>0.77826704680664749</v>
+          </cell>
+          <cell r="F6">
+            <v>2.1768526827455936</v>
+          </cell>
+          <cell r="G6">
+            <v>0.30272044989613406</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="E7">
+            <v>0.84486221613752133</v>
+          </cell>
+          <cell r="F7">
+            <v>2.464359288292099</v>
+          </cell>
+          <cell r="G7">
+            <v>0.31756193662124627</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="E8">
+            <v>0.91882162594644479</v>
+          </cell>
+          <cell r="F8">
+            <v>2.7060008232242336</v>
+          </cell>
+          <cell r="G8">
+            <v>0.39455673936365637</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="E9">
+            <v>0.96270546410180979</v>
+          </cell>
+          <cell r="F9">
+            <v>2.9274268362844258</v>
+          </cell>
+          <cell r="G9">
+            <v>0.44543294229516656</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="E10">
+            <v>1.0239640369866647</v>
+          </cell>
+          <cell r="F10">
+            <v>3.1256414735043663</v>
+          </cell>
+          <cell r="G10">
+            <v>0.51324424308392258</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="E11">
+            <v>1.0678330862343137</v>
+          </cell>
+          <cell r="F11">
+            <v>3.3018647321002264</v>
+          </cell>
+          <cell r="G11">
+            <v>0.56206673449545508</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="E12">
+            <v>1.1250190736565042</v>
+          </cell>
+          <cell r="F12">
+            <v>3.4711752869273647</v>
+          </cell>
+          <cell r="G12">
+            <v>0.59713550679772964</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="E13">
+            <v>1.2045784641095207</v>
+          </cell>
+          <cell r="F13">
+            <v>3.6268820043517778</v>
+          </cell>
+          <cell r="G13">
+            <v>0.62979682525550629</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="E14">
+            <v>1.2068987019193613</v>
+          </cell>
+          <cell r="F14">
+            <v>3.7693818979616709</v>
+          </cell>
+          <cell r="G14">
+            <v>0.67520073089069388</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="E15">
+            <v>1.2361844428801496</v>
+          </cell>
+          <cell r="F15">
+            <v>3.9046200224387309</v>
+          </cell>
+          <cell r="G15">
+            <v>0.70417626476122619</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="E16">
+            <v>1.259271263185658</v>
+          </cell>
+          <cell r="F16">
+            <v>4.0334210290741446</v>
+          </cell>
+          <cell r="G16">
+            <v>0.72892975334370924</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="E17">
+            <v>1.3012145316076791</v>
+          </cell>
+          <cell r="F17">
+            <v>4.1832130896040161</v>
+          </cell>
+          <cell r="G17">
+            <v>0.74462933325109992</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="E18">
+            <v>1.3255505532952461</v>
+          </cell>
+          <cell r="F18">
+            <v>4.2754123710177439</v>
+          </cell>
+          <cell r="G18">
+            <v>0.774786947269548</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19">
+            <v>1.3520956505279338</v>
+          </cell>
+          <cell r="F19">
+            <v>4.4002371006387984</v>
+          </cell>
+          <cell r="G19">
+            <v>0.79123436512436673</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="E20">
+            <v>1.3096110069525659</v>
+          </cell>
+          <cell r="F20">
+            <v>4.5676086152707969</v>
+          </cell>
+          <cell r="G20">
+            <v>0.82463991130814507</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/ra/dataCounters/counters.xlsx
+++ b/ra/dataCounters/counters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\uni\masters nu\RA\pythonCode\ra\dataCounters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC38E07-D2E2-49D5-8579-64BC21CCA0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F66BE00-EFAE-4E0B-899E-396410EEF85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14101,8 +14101,8 @@
       <sheetName val="90s 9000"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="2">
           <cell r="A2">
@@ -14200,237 +14200,15 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3">
-        <row r="1">
-          <cell r="E1" t="str">
-            <v>Log NE</v>
-          </cell>
-          <cell r="F1" t="str">
-            <v>Log LE</v>
-          </cell>
-          <cell r="G1" t="str">
-            <v>Log Ftst</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4">
-        <row r="2">
-          <cell r="E2">
-            <v>0.17912072960929923</v>
-          </cell>
-          <cell r="F2">
-            <v>0.36068075590673898</v>
-          </cell>
-          <cell r="G2">
-            <v>-0.38806437495987745</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="E3">
-            <v>0.26688993247105292</v>
-          </cell>
-          <cell r="F3">
-            <v>0.98361730349472876</v>
-          </cell>
-          <cell r="G3">
-            <v>-0.2277516600281464</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="E4">
-            <v>0.40859607646278268</v>
-          </cell>
-          <cell r="F4">
-            <v>1.4609198138946675</v>
-          </cell>
-          <cell r="G4">
-            <v>-8.6981316252039753E-2</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="E5">
-            <v>0.53064785352748556</v>
-          </cell>
-          <cell r="F5">
-            <v>1.8612580333896194</v>
-          </cell>
-          <cell r="G5">
-            <v>-9.7499670721832143E-3</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="E6">
-            <v>0.77826704680664749</v>
-          </cell>
-          <cell r="F6">
-            <v>2.1768526827455936</v>
-          </cell>
-          <cell r="G6">
-            <v>0.30272044989613406</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="E7">
-            <v>0.84486221613752133</v>
-          </cell>
-          <cell r="F7">
-            <v>2.464359288292099</v>
-          </cell>
-          <cell r="G7">
-            <v>0.31756193662124627</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="E8">
-            <v>0.91882162594644479</v>
-          </cell>
-          <cell r="F8">
-            <v>2.7060008232242336</v>
-          </cell>
-          <cell r="G8">
-            <v>0.39455673936365637</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="E9">
-            <v>0.96270546410180979</v>
-          </cell>
-          <cell r="F9">
-            <v>2.9274268362844258</v>
-          </cell>
-          <cell r="G9">
-            <v>0.44543294229516656</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="E10">
-            <v>1.0239640369866647</v>
-          </cell>
-          <cell r="F10">
-            <v>3.1256414735043663</v>
-          </cell>
-          <cell r="G10">
-            <v>0.51324424308392258</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="E11">
-            <v>1.0678330862343137</v>
-          </cell>
-          <cell r="F11">
-            <v>3.3018647321002264</v>
-          </cell>
-          <cell r="G11">
-            <v>0.56206673449545508</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="E12">
-            <v>1.1250190736565042</v>
-          </cell>
-          <cell r="F12">
-            <v>3.4711752869273647</v>
-          </cell>
-          <cell r="G12">
-            <v>0.59713550679772964</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="E13">
-            <v>1.2045784641095207</v>
-          </cell>
-          <cell r="F13">
-            <v>3.6268820043517778</v>
-          </cell>
-          <cell r="G13">
-            <v>0.62979682525550629</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="E14">
-            <v>1.2068987019193613</v>
-          </cell>
-          <cell r="F14">
-            <v>3.7693818979616709</v>
-          </cell>
-          <cell r="G14">
-            <v>0.67520073089069388</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="E15">
-            <v>1.2361844428801496</v>
-          </cell>
-          <cell r="F15">
-            <v>3.9046200224387309</v>
-          </cell>
-          <cell r="G15">
-            <v>0.70417626476122619</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="E16">
-            <v>1.259271263185658</v>
-          </cell>
-          <cell r="F16">
-            <v>4.0334210290741446</v>
-          </cell>
-          <cell r="G16">
-            <v>0.72892975334370924</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="E17">
-            <v>1.3012145316076791</v>
-          </cell>
-          <cell r="F17">
-            <v>4.1832130896040161</v>
-          </cell>
-          <cell r="G17">
-            <v>0.74462933325109992</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="E18">
-            <v>1.3255505532952461</v>
-          </cell>
-          <cell r="F18">
-            <v>4.2754123710177439</v>
-          </cell>
-          <cell r="G18">
-            <v>0.774786947269548</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="E19">
-            <v>1.3520956505279338</v>
-          </cell>
-          <cell r="F19">
-            <v>4.4002371006387984</v>
-          </cell>
-          <cell r="G19">
-            <v>0.79123436512436673</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="E20">
-            <v>1.3096110069525659</v>
-          </cell>
-          <cell r="F20">
-            <v>4.5676086152707969</v>
-          </cell>
-          <cell r="G20">
-            <v>0.82463991130814507</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
